--- a/output/regra_h_cnae_ocde.xlsx
+++ b/output/regra_h_cnae_ocde.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G104"/>
+  <dimension ref="A1:I104"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -390,6 +390,16 @@
           <t>ocde_class</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>alias_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>alias_2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -417,6 +427,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -444,6 +459,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -471,6 +491,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -498,6 +523,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -525,6 +555,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -552,6 +587,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -579,6 +619,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -606,6 +651,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -633,6 +683,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -660,6 +715,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -687,6 +747,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -714,6 +779,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -741,6 +811,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Fab. bens alimentícios, bebida e fumo</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -768,6 +843,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -795,6 +875,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -822,6 +907,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -849,6 +939,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -876,6 +971,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -903,6 +1003,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -930,6 +1035,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -957,6 +1067,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -984,6 +1099,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1011,6 +1131,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1038,6 +1163,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>Fab. têxteis, arts. vestuário, couro e calçados</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1065,6 +1195,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1092,6 +1227,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1119,6 +1259,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1146,6 +1291,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1173,6 +1323,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1200,6 +1355,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1227,6 +1387,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1254,6 +1419,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1281,6 +1451,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1308,6 +1483,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Fab. coque, prods, derivs. petróleo e biocombs.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1335,6 +1515,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Fab. coque, prods, derivs. petróleo e biocombs.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1362,6 +1547,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Fab. coque, prods, derivs. petróleo e biocombs.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1389,6 +1579,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1416,6 +1611,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1443,6 +1643,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1470,6 +1675,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1497,6 +1707,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1524,6 +1739,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1551,6 +1771,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1578,6 +1803,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Fab. de químicos (exc. farmacêuticos)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1605,6 +1835,11 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Indústria farmacêutica</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1632,6 +1867,11 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Indústria farmacêutica</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1659,6 +1899,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Fab. prods. borracha e mat. plástico</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1686,6 +1931,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Fab. prods. borracha e mat. plástico</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1713,6 +1963,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Fab. prods. minerais não-metáls.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1740,6 +1995,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Fab. prods. minerais não-metáls.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1767,6 +2027,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Fab. prods. minerais não-metáls.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1794,6 +2059,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>Fab. prods. minerais não-metáls.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -1821,6 +2091,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Fab. prods. minerais não-metáls.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -1848,6 +2123,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Metalurgia</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -1875,6 +2155,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Metalurgia</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -1902,6 +2187,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Metalurgia</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -1929,6 +2219,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Metalurgia</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -1956,6 +2251,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Metalurgia</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -1984,6 +2284,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Fab. prods. de metal</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2011,6 +2316,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Fab. prods. de metal</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2038,6 +2348,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>Fab. prods. de metal</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2065,6 +2380,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Fab. prods. de metal</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2092,6 +2412,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>Fab. equip. bélicos pesados, armas e munição</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2119,6 +2444,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Fab. prods. de metal</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2146,6 +2476,11 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2173,6 +2508,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>Material de escritório e informática</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2200,6 +2545,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>Material de escritório e informática</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2227,6 +2582,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>Equipamento de rádio, tv e comunicação</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2254,6 +2619,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>Instrumentos médicos, de ótica e precisão</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2281,6 +2656,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>Instrumentos médicos, de ótica e precisão</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2308,6 +2693,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>Instrumentos médicos, de ótica e precisão</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2335,6 +2730,16 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Complexo eletrônico</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>Instrumentos médicos, de ótica e precisão</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2362,6 +2767,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2389,6 +2799,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2416,6 +2831,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2443,6 +2863,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2470,6 +2895,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2497,6 +2927,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Fab. máqs., apars. e maters. elétricos</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2524,6 +2959,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2551,6 +2991,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2578,6 +3023,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -2605,6 +3055,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -2632,6 +3087,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -2659,6 +3119,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Fab. M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -2686,6 +3151,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Fab. veícs. automotores, reboqs. e carrocerias</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -2713,6 +3183,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>Fab. veícs. automotores, reboqs. e carrocerias</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -2740,6 +3215,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Fab. veícs. automotores, reboqs. e carrocerias</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -2767,6 +3247,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>Fab. veícs. automotores, reboqs. e carrocerias</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -2794,6 +3279,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Fab. veícs. automotores, reboqs. e carrocerias</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -2821,6 +3311,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Fab. de embarcações</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -2848,6 +3343,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Fab. de veícs. ferrov., militares e não espec.</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -2875,6 +3375,11 @@
           <t>Alta</t>
         </is>
       </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Fabricação de aeronaves</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -2902,6 +3407,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Fab. de veícs. ferrov., militares e não espec.</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -2929,6 +3439,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Fab. de veícs. ferrov., militares e não espec.</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -2956,6 +3471,11 @@
           <t>Média Baixa</t>
         </is>
       </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Fab. prods. madeira, móveis, papel, celulose, impress.</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -2983,6 +3503,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Fab. bens diversos (exc. I&amp;M)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3010,6 +3535,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Fab. bens diversos (exc. I&amp;M)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3037,6 +3567,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Fab. bens diversos (exc. I&amp;M)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -3064,6 +3599,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>Fab. bens diversos (exc. I&amp;M)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -3091,6 +3631,11 @@
           <t>Média Alta</t>
         </is>
       </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>Fab. I&amp;M uso médico e odontolog., arts. óticos</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -3118,6 +3663,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>Fab. bens diversos (exc. I&amp;M)</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -3145,6 +3695,11 @@
           <t>Média</t>
         </is>
       </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>Manutenç., reparaç., intalaç. de M&amp;E</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -3170,6 +3725,11 @@
       <c r="G104" t="inlineStr">
         <is>
           <t>Média</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>Manutenç., reparaç., intalaç. de M&amp;E</t>
         </is>
       </c>
     </row>
